--- a/business_surveys/017_sector_icons_feedback_survey--business_surveys.xlsx
+++ b/business_surveys/017_sector_icons_feedback_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sector_icons_feedback_survey</t>
+          <t>sector_icon_effectiveness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sector_icons_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Which of the sector icons is the most effective in communicating the organization's identity?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select the most effective sector icon.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,48 +547,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>overall_design_effectiveness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How would you rate the overall design effectiveness of the sector icons?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please rate on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>icon_design_effectiveness</t>
+          <t>icon_design_improvement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>icon_design_effectiveness</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What specific improvements could be made to the icon design itself?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide detailed feedback.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,33 +606,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>user_insights</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What kind of insights do you get when looking at the sector icons?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide detailed feedback.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>branding_and_user_interface</t>
+          <t>overall_user_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>branding_and_user_interface</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How does the sector icon contribute to the overall user experience?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please rate on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -635,38 +655,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>icon_improvement</t>
+          <t>icon_quality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>icon_improvement</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What would you rate the quality of the sector icon design?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please rate on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Which organization is using sector icons?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select the organization.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>icon_style</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the design style of the sector icon?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select from Modern, Classic, or Minimalist.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>icon_color_scheme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the color scheme of the sector icon?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select from Monochromatic, Multicolored, or Grayscale.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>icon_design_style</t>
+          <t>icon_scale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>icon_design_style</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the size of the sector icon?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select from Small, Medium, or Large.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>icon_color_scheme</t>
+          <t>icon_feeling</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>icon_color_scheme</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How does the sector icon make you feel?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select from Not at all, Somewhat, Very, or Extremely.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>icon_scale</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>icon_scale</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What specific feedback have you received about the sector icon?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide detailed feedback.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>icon_feeling</t>
+          <t>organization_surveyed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>icon_feeling</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Which organization is being surveyed in this sector icon feedback?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select the organization.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -814,46 +866,54 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>organization_surveyed</t>
+          <t>sector_improvement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>organization_surveyed</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Is there an improvement that could be made to the color scheme of the sector icon?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please select from Yes or No.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>icon_design_improvement</t>
+          <t>overall_improvement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>icon_design_improvement</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Are there any overall improvements that could be made to the sector icon design?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please select from Yes or No.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>icon_color_scheme_improvement</t>
+          <t>user_interface_improvement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>icon_color_scheme_improvement</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What specific improvement could be made to the overall user interface?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide detailed feedback.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,205 +947,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>icon_feeling_improvement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>What specific improvement could be made to the sector icon design itself?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide detailed feedback.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_interface_improvement</t>
+          <t>user_experience_improvement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>user_interface_improvement</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>User Experience Improvement</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please select from Not at all, Somewhat, Very, or Extremely.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>icon_feeling_improvement</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>icon_feeling_improvement</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>overall_improvement</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>overall_improvement</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>icon_improvement</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>icon_improvement</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>icon_scale_improvement</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>icon_scale_improvement</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>feedback_improvement</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>feedback_improvement</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +1013,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,510 +1037,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>icon_design_effectiveness_choices</t>
+          <t>sector_icon_effectiveness_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>sector_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all'}</t>
+          <t>Sector 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>icon_design_effectiveness_choices</t>
+          <t>sector_icon_effectiveness_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat'}</t>
+          <t>sector_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat'}</t>
+          <t>Sector 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>icon_design_effectiveness_choices</t>
+          <t>sector_icon_effectiveness_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'very'}</t>
+          <t>sector_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Very'}</t>
+          <t>Sector 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>icon_design_effectiveness_choices</t>
+          <t>organization_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'extremely'}</t>
+          <t>company_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Extremely'}</t>
+          <t>Company A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>branding_and_user_interface_choices</t>
+          <t>organization_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>company_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all'}</t>
+          <t>Company B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>branding_and_user_interface_choices</t>
+          <t>organization_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>branding_and_user_interface_choices</t>
+          <t>icon_style_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'very'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Very'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>branding_and_user_interface_choices</t>
+          <t>icon_style_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'extremely'}</t>
+          <t>classic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Extremely'}</t>
+          <t>Classic</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_choices</t>
+          <t>icon_style_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'company_a'}</t>
+          <t>minimalist</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Company A'}</t>
+          <t>Minimalist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_choices</t>
+          <t>icon_color_scheme_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'company_b'}</t>
+          <t>monochromatic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Company B'}</t>
+          <t>Monochromatic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_choices</t>
+          <t>icon_color_scheme_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>multicolored</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Multicolored</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>icon_design_style_choices</t>
+          <t>icon_color_scheme_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'modern'}</t>
+          <t>grayscale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Modern'}</t>
+          <t>Grayscale</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>icon_design_style_choices</t>
+          <t>icon_scale_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'classic'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Classic'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>icon_design_style_choices</t>
+          <t>icon_scale_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'minimalist'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Minimalist'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>icon_color_scheme_choices</t>
+          <t>icon_scale_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'monochromatic'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Monochromatic'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>icon_color_scheme_choices</t>
+          <t>icon_feeling_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'multicolored'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Multicolored'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>icon_color_scheme_choices</t>
+          <t>icon_feeling_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'grayscale'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Grayscale'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>icon_scale_choices</t>
+          <t>icon_feeling_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'small'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Small'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>icon_scale_choices</t>
+          <t>icon_feeling_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>icon_scale_choices</t>
+          <t>organization_surveyed_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'large'}</t>
+          <t>company_a</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Large'}</t>
+          <t>Company A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>icon_feeling_choices</t>
+          <t>organization_surveyed_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>company_b</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all'}</t>
+          <t>Company B</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>icon_feeling_choices</t>
+          <t>organization_surveyed_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>icon_feeling_choices</t>
+          <t>sector_improvement_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'very'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Very'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>icon_feeling_choices</t>
+          <t>sector_improvement_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'extremely'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Extremely'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_surveyed_choices</t>
+          <t>overall_improvement_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'sector_1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Sector 1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_surveyed_choices</t>
+          <t>overall_improvement_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'sector_2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Sector 2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_surveyed_choices</t>
+          <t>user_experience_improvement_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'sector_3'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Sector 3'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sector_choices</t>
+          <t>user_experience_improvement_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'sector_1'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Sector 1'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sector_choices</t>
+          <t>user_experience_improvement_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'sector_2'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Sector 2'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sector_choices</t>
+          <t>user_experience_improvement_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'sector_3'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Sector 3'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
